--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110536</v>
+        <v>110542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,57 +1208,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B7" t="n">
-        <v>98414</v>
+        <v>109266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R7" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,7 +1292,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1319,48 +1310,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304841</v>
+        <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>109260</v>
+        <v>98420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698804</v>
+        <v>698818</v>
       </c>
       <c r="R8" t="n">
-        <v>6389073</v>
+        <v>6389134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304848</v>
       </c>
       <c r="B10" t="n">
-        <v>99187</v>
+        <v>99193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>127304846</v>
       </c>
       <c r="B11" t="n">
-        <v>99111</v>
+        <v>99117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -893,48 +893,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>109266</v>
+        <v>98420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R4" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -995,57 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>98420</v>
+        <v>109266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R5" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,48 +1106,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304844</v>
+        <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>109266</v>
+        <v>98420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R6" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1208,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304841</v>
+        <v>127304844</v>
       </c>
       <c r="B7" t="n">
         <v>109266</v>
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698804</v>
+        <v>698808</v>
       </c>
       <c r="R7" t="n">
-        <v>6389073</v>
+        <v>6389075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1301,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,57 +1319,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>98420</v>
+        <v>109266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R8" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127304848</v>
+        <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99193</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698818</v>
+        <v>698832</v>
       </c>
       <c r="R10" t="n">
-        <v>6389134</v>
+        <v>6389100</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,11 +1601,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1617,7 +1612,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Porsmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1635,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304846</v>
+        <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99117</v>
+        <v>99193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1641,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,13 +1665,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698832</v>
+        <v>698818</v>
       </c>
       <c r="R11" t="n">
-        <v>6389100</v>
+        <v>6389134</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,6 +1703,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Porsmyr.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110542</v>
+        <v>110543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,57 +1106,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304851</v>
+        <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>98420</v>
+        <v>109267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R6" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1217,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304844</v>
+        <v>127304841</v>
       </c>
       <c r="B7" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698808</v>
+        <v>698804</v>
       </c>
       <c r="R7" t="n">
-        <v>6389075</v>
+        <v>6389073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1292,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1319,48 +1310,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304841</v>
+        <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>109266</v>
+        <v>98421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698804</v>
+        <v>698818</v>
       </c>
       <c r="R8" t="n">
-        <v>6389073</v>
+        <v>6389134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99193</v>
+        <v>99194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -1106,48 +1106,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304844</v>
+        <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>109267</v>
+        <v>98421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R6" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1208,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304841</v>
+        <v>127304844</v>
       </c>
       <c r="B7" t="n">
         <v>109267</v>
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698804</v>
+        <v>698808</v>
       </c>
       <c r="R7" t="n">
-        <v>6389073</v>
+        <v>6389075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1301,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,57 +1319,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>98421</v>
+        <v>109267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R8" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110543</v>
+        <v>110549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,57 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>98421</v>
+        <v>109273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R4" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,48 +995,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>109267</v>
+        <v>98425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R5" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
         <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99194</v>
+        <v>99198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110549</v>
+        <v>110551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,48 +893,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>109273</v>
+        <v>98426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R4" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -995,57 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>98425</v>
+        <v>109275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R5" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
         <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99122</v>
+        <v>99123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127304846</v>
+        <v>127304848</v>
       </c>
       <c r="B10" t="n">
-        <v>99123</v>
+        <v>99199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698832</v>
+        <v>698818</v>
       </c>
       <c r="R10" t="n">
-        <v>6389100</v>
+        <v>6389134</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,6 +1601,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Porsmyr.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1630,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304848</v>
+        <v>127304846</v>
       </c>
       <c r="B11" t="n">
-        <v>99199</v>
+        <v>99123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,13 +1670,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698818</v>
+        <v>698832</v>
       </c>
       <c r="R11" t="n">
-        <v>6389134</v>
+        <v>6389100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,11 +1708,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Porsmyr.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110551</v>
+        <v>110553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,57 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>98426</v>
+        <v>109277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R4" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,48 +995,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>109275</v>
+        <v>98428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R5" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,57 +1106,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304851</v>
+        <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>98426</v>
+        <v>109277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R6" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1217,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304844</v>
+        <v>127304841</v>
       </c>
       <c r="B7" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698808</v>
+        <v>698804</v>
       </c>
       <c r="R7" t="n">
-        <v>6389075</v>
+        <v>6389073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1292,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1319,48 +1310,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304841</v>
+        <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>109275</v>
+        <v>98428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698804</v>
+        <v>698818</v>
       </c>
       <c r="R8" t="n">
-        <v>6389073</v>
+        <v>6389134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127304848</v>
+        <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99199</v>
+        <v>99125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698818</v>
+        <v>698832</v>
       </c>
       <c r="R10" t="n">
-        <v>6389134</v>
+        <v>6389100</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,11 +1601,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1617,7 +1612,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Porsmyr.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1635,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304846</v>
+        <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99123</v>
+        <v>99201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1641,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,13 +1665,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698832</v>
+        <v>698818</v>
       </c>
       <c r="R11" t="n">
-        <v>6389100</v>
+        <v>6389134</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,6 +1703,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Porsmyr.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -893,48 +893,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>109277</v>
+        <v>98428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R4" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -995,57 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R5" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,48 +1106,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304844</v>
+        <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>109277</v>
+        <v>98428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R6" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1208,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304841</v>
+        <v>127304844</v>
       </c>
       <c r="B7" t="n">
         <v>109277</v>
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698804</v>
+        <v>698808</v>
       </c>
       <c r="R7" t="n">
-        <v>6389073</v>
+        <v>6389075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1301,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,57 +1319,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R8" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -893,57 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R4" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,48 +995,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>109277</v>
+        <v>98428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R5" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,57 +1106,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304851</v>
+        <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>98428</v>
+        <v>109277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R6" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1217,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304844</v>
+        <v>127304841</v>
       </c>
       <c r="B7" t="n">
         <v>109277</v>
@@ -1252,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698808</v>
+        <v>698804</v>
       </c>
       <c r="R7" t="n">
-        <v>6389075</v>
+        <v>6389073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1292,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1319,48 +1310,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304841</v>
+        <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>109277</v>
+        <v>98428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698804</v>
+        <v>698818</v>
       </c>
       <c r="R8" t="n">
-        <v>6389073</v>
+        <v>6389134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110553</v>
+        <v>110559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127304841</v>
       </c>
       <c r="B7" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99125</v>
+        <v>99131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99201</v>
+        <v>99207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110559</v>
+        <v>110562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127304841</v>
       </c>
       <c r="B7" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>127304851</v>
       </c>
       <c r="B8" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99131</v>
+        <v>99134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99207</v>
+        <v>99210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110562</v>
+        <v>110570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,48 +893,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>109286</v>
+        <v>98445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R4" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -995,57 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>98437</v>
+        <v>109294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R5" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,48 +1106,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304844</v>
+        <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>109286</v>
+        <v>98445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R6" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1208,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304841</v>
+        <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698804</v>
+        <v>698808</v>
       </c>
       <c r="R7" t="n">
-        <v>6389073</v>
+        <v>6389075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1301,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,57 +1319,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>98437</v>
+        <v>109294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R8" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99134</v>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99210</v>
+        <v>99218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110570</v>
+        <v>110571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99142</v>
+        <v>99143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99218</v>
+        <v>99219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110571</v>
+        <v>110572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127304850</v>
       </c>
       <c r="B5" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>127304851</v>
       </c>
       <c r="B6" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>127304846</v>
       </c>
       <c r="B10" t="n">
-        <v>99143</v>
+        <v>99144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>127304848</v>
       </c>
       <c r="B11" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127304837</v>
       </c>
       <c r="B2" t="n">
-        <v>110572</v>
+        <v>110536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127304853</v>
       </c>
       <c r="B3" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,57 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127304845</v>
+        <v>127304850</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>109260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R4" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,48 +995,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304850</v>
+        <v>127304845</v>
       </c>
       <c r="B5" t="n">
-        <v>109296</v>
+        <v>98414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R5" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1106,57 +1106,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304851</v>
+        <v>127304844</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>109260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698818</v>
+        <v>698808</v>
       </c>
       <c r="R6" t="n">
-        <v>6389134</v>
+        <v>6389075</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Tallsumpskog, träd på socklar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1217,48 +1208,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304844</v>
+        <v>127304851</v>
       </c>
       <c r="B7" t="n">
-        <v>109296</v>
+        <v>98414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698808</v>
+        <v>698818</v>
       </c>
       <c r="R7" t="n">
-        <v>6389075</v>
+        <v>6389134</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallsumpskog, träd på socklar.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         <v>127304841</v>
       </c>
       <c r="B8" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127304858</v>
       </c>
       <c r="B9" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127304846</v>
+        <v>127304848</v>
       </c>
       <c r="B10" t="n">
-        <v>99144</v>
+        <v>99187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698832</v>
+        <v>698818</v>
       </c>
       <c r="R10" t="n">
-        <v>6389100</v>
+        <v>6389134</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,6 +1601,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Porsmyr.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1630,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304848</v>
+        <v>127304846</v>
       </c>
       <c r="B11" t="n">
-        <v>99220</v>
+        <v>99111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1665,13 +1670,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698818</v>
+        <v>698832</v>
       </c>
       <c r="R11" t="n">
-        <v>6389134</v>
+        <v>6389100</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,11 +1708,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Porsmyr.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127304837</v>
+        <v>127304863</v>
       </c>
       <c r="B2" t="n">
-        <v>110572</v>
+        <v>106122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219716</v>
+        <v>50</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Knutört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Lysimachia minima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
+          <t>Prästgården 1:1 (4), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698779</v>
+        <v>698727</v>
       </c>
       <c r="R2" t="n">
-        <v>6389063</v>
+        <v>6389097</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera ex med flera stänglar.</t>
+          <t>Gränsområde mot Björkebos 1:7 (3)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Glänta, fuktig.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127304853</v>
+        <v>127304837</v>
       </c>
       <c r="B3" t="n">
-        <v>109296</v>
+        <v>111399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219716</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698801</v>
+        <v>698779</v>
       </c>
       <c r="R3" t="n">
-        <v>6389158</v>
+        <v>6389063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +864,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera ex med flera stänglar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,7 +880,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Glänta, fuktig.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -896,7 +901,7 @@
         <v>127304845</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,35 +1009,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127304850</v>
+        <v>127304851</v>
       </c>
       <c r="B5" t="n">
-        <v>109296</v>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
@@ -1106,57 +1120,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127304851</v>
+        <v>127304841</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698818</v>
+        <v>698804</v>
       </c>
       <c r="R6" t="n">
-        <v>6389134</v>
+        <v>6389073</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1204,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,7 +1225,7 @@
         <v>127304844</v>
       </c>
       <c r="B7" t="n">
-        <v>109296</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127304841</v>
+        <v>127304850</v>
       </c>
       <c r="B8" t="n">
-        <v>109296</v>
+        <v>110078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,13 +1359,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698804</v>
+        <v>698818</v>
       </c>
       <c r="R8" t="n">
-        <v>6389073</v>
+        <v>6389134</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1408,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig.</t>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1421,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127304858</v>
+        <v>127304853</v>
       </c>
       <c r="B9" t="n">
-        <v>109296</v>
+        <v>110078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,13 +1461,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698773</v>
+        <v>698801</v>
       </c>
       <c r="R9" t="n">
-        <v>6389174</v>
+        <v>6389158</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,11 +1497,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gränsområde mot Prästgården 1:11 (4).</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127304846</v>
+        <v>127304858</v>
       </c>
       <c r="B10" t="n">
-        <v>99144</v>
+        <v>110078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698832</v>
+        <v>698773</v>
       </c>
       <c r="R10" t="n">
-        <v>6389100</v>
+        <v>6389174</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,6 +1601,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gränsområde mot Prästgården 1:11 (4).</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Porsmyr.</t>
+          <t>Barrskog, fuktig.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1630,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127304848</v>
+        <v>127304868</v>
       </c>
       <c r="B11" t="n">
-        <v>99220</v>
+        <v>110078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,16 +1646,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222361</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1661,17 +1666,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
+          <t>Prästgården 1:1 (4), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698818</v>
+        <v>698727</v>
       </c>
       <c r="R11" t="n">
-        <v>6389134</v>
+        <v>6389097</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,7 +1710,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Gränsområde mot Björkebos 1:7 (3)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,7 +1724,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+          <t>Glänta, fuktig.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1734,6 +1739,661 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127304865</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Prästgården 1:1 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698727</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6389097</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gränsområde mot Björkebos 1:7 (3)</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127304875</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Prästgården 1:1 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698714</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6389080</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gränsområde mot Björkebos 1:7 (3)</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Glänta, fuktig.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127304846</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698832</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6389100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Porsmyr.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127304856</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698734</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6389160</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gränsområde mot Prästgården 1:11 (4).</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrskog, fuktig.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127304869</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Prästgården 1:1 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698727</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6389097</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gränsområde mot Björkebos 1:7 (3)</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Glänta, fuktig.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127304848</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björkebos 1:7 (3) A 35293-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698818</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6389134</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrskog, fuktig. Blåtåtelsumpskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35293-2025 artfynd.xlsx
+++ b/artfynd/A 35293-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304844</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304850</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304853</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304858</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304868</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304865</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304875</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2055,6 +2120,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304846</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304856</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304869</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,8 +2474,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>